--- a/public/sap-reporting/expansion-150-downloads/EXT-CO19-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-CO19-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R2387c912ccdb48e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R9c348ba730d24b13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R021cd16dd58b4e0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rcdf3d556cd084340"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R1e7dd2f9805a4da6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R4a2d9f52fd354dd5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1266,7 +1266,7 @@
         <x:v>Giữ chuỗi RAW và locale. Chuẩn hóa dấu, separator, currency/UoM/price unit trước tính. Blank không là0; không cộng tỷ lệ/đơn giá/snapshot.</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="63" customHeight="1">
+    <x:row r="13" ht="80" customHeight="1">
       <x:c r="A13" s="8" t="str">
         <x:v>12</x:v>
       </x:c>
@@ -1274,7 +1274,7 @@
         <x:v>Price Unit</x:v>
       </x:c>
       <x:c r="C13" s="8" t="str">
-        <x:v>text</x:v>
+        <x:v>raw_decimal</x:v>
       </x:c>
       <x:c r="D13" s="8" t="str">
         <x:v>Số đơn vị làm mẫu số của đơn giá</x:v>
@@ -1283,7 +1283,7 @@
         <x:v>SAVA_PROPOSED / chưa xác minh</x:v>
       </x:c>
       <x:c r="F13" s="8" t="str">
-        <x:v>Giữ ID dạng Text và số0 đầu. Trim trên bản CLEAN riêng, giữ raw value và source-row lineage. Không join bằng tên diễn giải.</x:v>
+        <x:v>Giữ chuỗi RAW và locale. Chuẩn hóa dấu, separator, currency/UoM/price unit trước tính. Blank không là0; không cộng tỷ lệ/đơn giá/snapshot.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="63" customHeight="1">
